--- a/rss_islandr/templates/results - Copy.xlsx
+++ b/rss_islandr/templates/results - Copy.xlsx
@@ -9,75 +9,168 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="50">
   <si>
     <t>Soil</t>
   </si>
   <si>
-    <t>Industrial</t>
+    <t>Surface water</t>
+  </si>
+  <si>
+    <t>Source-pathway-receptor analysis</t>
+  </si>
+  <si>
+    <t>Site Name</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Primary Industry</t>
+  </si>
+  <si>
+    <t>Source - Industry</t>
+  </si>
+  <si>
+    <t>Toxicity</t>
+  </si>
+  <si>
+    <t>Extent</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Pathways</t>
+  </si>
+  <si>
+    <t>Ground water</t>
+  </si>
+  <si>
+    <t>Air</t>
+  </si>
+  <si>
+    <t>Sediment</t>
+  </si>
+  <si>
+    <t>Containment</t>
+  </si>
+  <si>
+    <t>Surface cover</t>
+  </si>
+  <si>
+    <t>Soil permeability</t>
+  </si>
+  <si>
+    <t>Depth to hazard</t>
+  </si>
+  <si>
+    <t>Permeability Layer</t>
+  </si>
+  <si>
+    <t>Distance to user</t>
+  </si>
+  <si>
+    <t>Flood potential</t>
+  </si>
+  <si>
+    <t>Emission type</t>
+  </si>
+  <si>
+    <t>Distance to population</t>
+  </si>
+  <si>
+    <t>Particle size</t>
+  </si>
+  <si>
+    <t>Contamination level</t>
+  </si>
+  <si>
+    <t>Water interaction</t>
+  </si>
+  <si>
+    <t>Sediment type</t>
+  </si>
+  <si>
+    <t>Receptors</t>
+  </si>
+  <si>
+    <t>Pathway</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Total Risk</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>Unconfined</t>
   </si>
   <si>
     <t>Significant waterway</t>
   </si>
   <si>
+    <t>Bio-accumulative and toxic materials</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>No limit to access</t>
+  </si>
+  <si>
+    <t>&lt;1m</t>
+  </si>
+  <si>
+    <t>Value Not Known</t>
+  </si>
+  <si>
+    <t>Silt/clay aquifer: 20m</t>
+  </si>
+  <si>
+    <t>Point source</t>
+  </si>
+  <si>
+    <t>&lt;1km</t>
+  </si>
+  <si>
+    <t>PM10</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Domestic/potable</t>
+  </si>
+  <si>
+    <t>Option 2</t>
+  </si>
+  <si>
     <t>Option 1</t>
-  </si>
-  <si>
-    <t>Surface water</t>
-  </si>
-  <si>
-    <t>Bio-accumulative and toxic materials</t>
-  </si>
-  <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>No limit to access</t>
-  </si>
-  <si>
-    <t>&lt;1m</t>
-  </si>
-  <si>
-    <t>Unconfined</t>
-  </si>
-  <si>
-    <t>Silt/clay aquifer: 20m</t>
-  </si>
-  <si>
-    <t>Mobile source</t>
-  </si>
-  <si>
-    <t>1km-5km</t>
-  </si>
-  <si>
-    <t>PM10</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Frequent</t>
-  </si>
-  <si>
-    <t>Gravel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,16 +178,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -102,15 +230,570 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Calculation" xfId="3" builtinId="22"/>
+    <cellStyle name="Input" xfId="2" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -412,160 +1095,667 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1" spans="1:15" ht="23.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="31"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" ht="23.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="31"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B6" s="37"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="9"/>
+    </row>
+    <row r="10" spans="1:15" ht="23.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="31"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K11" s="23"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="35"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" s="35"/>
+      <c r="O12" s="16"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="28"/>
+      <c r="C13" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="28"/>
+      <c r="F13" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="28"/>
+      <c r="I13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="37"/>
+      <c r="L13" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="37"/>
+      <c r="O13" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B14" s="28"/>
+      <c r="C14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="I14" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="37"/>
+      <c r="L14" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="37"/>
+      <c r="O14" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B15" s="28"/>
+      <c r="C15" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="28"/>
+      <c r="F15" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="33"/>
+      <c r="I15" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="37"/>
+      <c r="L15" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="37"/>
+      <c r="O15" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="33"/>
+      <c r="F16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="15"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="7">
         <v>0</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="J16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="33"/>
+      <c r="L16" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16" s="33"/>
+      <c r="O16" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="14">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="23.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="31"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="str">
+        <f>A11</f>
+        <v>Soil</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="22" t="str">
+        <f t="shared" ref="D19" si="0">D11</f>
+        <v>Ground water</v>
+      </c>
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="22" t="str">
+        <f t="shared" ref="G19" si="1">G11</f>
+        <v>Surface water</v>
+      </c>
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="22" t="str">
+        <f t="shared" ref="J19" si="2">J11</f>
+        <v>Air</v>
+      </c>
+      <c r="K19" s="23"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="22" t="str">
+        <f t="shared" ref="M19" si="3">M11</f>
+        <v>Sediment</v>
+      </c>
+      <c r="N19" s="23"/>
+      <c r="O19" s="24"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D5">
+      <c r="D20" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
+      <c r="E20" s="26"/>
+      <c r="F20" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="G20" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="26"/>
+      <c r="I20" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="26"/>
+      <c r="L20" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="26"/>
+      <c r="O20" s="17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="28"/>
+      <c r="C21" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="28"/>
+      <c r="I21" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="28"/>
+      <c r="L21" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N21" s="28"/>
+      <c r="O21" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="19">
         <v>0</v>
       </c>
-      <c r="F6">
+      <c r="D22" s="20">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7">
+      <c r="E22" s="21"/>
+      <c r="F22" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+      <c r="G22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="19">
         <v>0</v>
       </c>
-      <c r="C20" t="s">
+      <c r="J22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="21"/>
+      <c r="L22" s="19">
         <v>0</v>
       </c>
-      <c r="D20" t="s">
+      <c r="M22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" s="21"/>
+      <c r="O22" s="10">
         <v>0</v>
       </c>
-      <c r="E20" t="s">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="61">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>